--- a/0_documents/sample.xlsx
+++ b/0_documents/sample.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Documents\cheat_sheets\1_lessons\code_institute\UDP5WA4CF-UN03_back_end_development\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Documents\cheat_sheets\1_lessons\code_institute\UDP5WA4CF-UN03_back_end_development\0_documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2B764A4-E593-46D7-B5B2-7EDDCCE444EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A8B9AFB-F28D-4867-A701-E815D28155E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C62C3A13-8B1D-4627-A4E5-0D3E0B3409FC}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="4" xr2:uid="{C62C3A13-8B1D-4627-A4E5-0D3E0B3409FC}"/>
   </bookViews>
   <sheets>
     <sheet name="original_copy-paste_sample" sheetId="1" r:id="rId1"/>
     <sheet name="reformat" sheetId="2" r:id="rId2"/>
     <sheet name="pivot_type" sheetId="3" r:id="rId3"/>
     <sheet name="pivot_time" sheetId="5" r:id="rId4"/>
+    <sheet name="questions-tests" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId5"/>
+    <pivotCache cacheId="0" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="99">
   <si>
     <t>PILA3</t>
   </si>
@@ -222,6 +223,120 @@
   </si>
   <si>
     <t>correct_answer</t>
+  </si>
+  <si>
+    <t>Questions\Tests</t>
+  </si>
+  <si>
+    <t>In history, how has social views affected the formation of legislation in regards to animals?</t>
+  </si>
+  <si>
+    <t>What is the main ethical framework of ASPA?</t>
+  </si>
+  <si>
+    <t>How are programmes of work ethically justified on a project licence?</t>
+  </si>
+  <si>
+    <t>What is the definition of the 3Rs?</t>
+  </si>
+  <si>
+    <t>How is pain, suffering, and distress typically interpreted and applied under ASPA?</t>
+  </si>
+  <si>
+    <t>What of the following can be considered to be a poor example of a culture of care?</t>
+  </si>
+  <si>
+    <t>Which of the following is one of the purposes of the local AWERB?</t>
+  </si>
+  <si>
+    <t>The use of animals in research is a controversial one and researchers have an obligation to ens...</t>
+  </si>
+  <si>
+    <t>Removing tissue from a live animal for genotyping is a common procedure in laboratory animal…</t>
+  </si>
+  <si>
+    <t>In the last three centuries, British legislation has slowly created more rights for animals. Today, …</t>
+  </si>
+  <si>
+    <t>All users of animals for scientific purposes have a legal and ethical obligation to ensure respon…</t>
+  </si>
+  <si>
+    <t>Which of the following is one of the primary statutory tasks of the Animal Welfare and Ethical R…</t>
+  </si>
+  <si>
+    <t>Over an animal’s lifetime, it will experience various types of suffering. These may be caused by t…</t>
+  </si>
+  <si>
+    <t>Users of animals models for research are expected to maintain high standards of animal welfar…</t>
+  </si>
+  <si>
+    <t>Those working with research animals have a responsibility to treat the animals in their care hu…</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>E1 LO1 MC1</t>
+  </si>
+  <si>
+    <t>E1 LO2 MC1</t>
+  </si>
+  <si>
+    <t>E1 LO2 MC2</t>
+  </si>
+  <si>
+    <t>E1 LO3 MC1</t>
+  </si>
+  <si>
+    <t>E1 LO4 MC2</t>
+  </si>
+  <si>
+    <t>E1 LO5 MC1</t>
+  </si>
+  <si>
+    <t>E1 LO6 MC1</t>
+  </si>
+  <si>
+    <t>E1 LO7 MC2</t>
+  </si>
+  <si>
+    <t>E1 LO8 MC1</t>
+  </si>
+  <si>
+    <t>E1 LO9 MC1</t>
+  </si>
+  <si>
+    <t>E1 LO10 MC1</t>
+  </si>
+  <si>
+    <t>E1 LO10 MC2</t>
+  </si>
+  <si>
+    <t>E1 LO12 MC1</t>
+  </si>
+  <si>
+    <t>E1 LO13 MC1</t>
+  </si>
+  <si>
+    <t>E1 LO14 MC1</t>
+  </si>
+  <si>
+    <t>jan-24-resit</t>
+  </si>
+  <si>
+    <t>jan-24</t>
+  </si>
+  <si>
+    <t>feb-24</t>
+  </si>
+  <si>
+    <t>feb-24-resit</t>
+  </si>
+  <si>
+    <t>apr-24</t>
+  </si>
+  <si>
+    <t>apr-24-resit</t>
   </si>
 </sst>
 </file>
@@ -1138,7 +1253,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="185">
+  <cellXfs count="189">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1363,34 +1478,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="39" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="39" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="39" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="39" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="4" xfId="9" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="39" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="39" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="39" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="39" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="39" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="39" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="37" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="37" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="40" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="40" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="40" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="40" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="39" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="39" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="39" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="39" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="37" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="39" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="39" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="39" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="39" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="37" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="39" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="39" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="39" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="39" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="19" fillId="39" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1400,13 +1512,15 @@
     <xf numFmtId="0" fontId="18" fillId="37" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="40" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="40" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="39" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="39" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="40" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="40" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="27" fillId="37" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="40" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="40" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="40" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="40" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="27" fillId="40" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1419,21 +1533,28 @@
     <xf numFmtId="0" fontId="29" fillId="39" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="37" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="40" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="40" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="40" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="40" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="23" fillId="37" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="39" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="39" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="4" xfId="9" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="18" fillId="39" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="39" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="39" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="39" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="37" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="39" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="39" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="39" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="39" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="37" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="5"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="17" fontId="5" fillId="0" borderId="0" xfId="5" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="5" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -3233,12 +3354,12 @@
     <dataField name="Average of incorrect_choice_percentage" fld="9" subtotal="average" baseField="0" baseItem="0"/>
   </dataFields>
   <conditionalFormats count="2">
-    <conditionalFormat priority="2">
+    <conditionalFormat priority="1">
       <pivotAreas count="1">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="2">
             <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
+              <x v="1"/>
             </reference>
             <reference field="0" count="6">
               <x v="0"/>
@@ -3252,12 +3373,12 @@
         </pivotArea>
       </pivotAreas>
     </conditionalFormat>
-    <conditionalFormat priority="1">
+    <conditionalFormat priority="2">
       <pivotAreas count="1">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="2">
             <reference field="4294967294" count="1" selected="0">
-              <x v="1"/>
+              <x v="0"/>
             </reference>
             <reference field="0" count="6">
               <x v="0"/>
@@ -3760,6 +3881,70 @@
     <dataField name="Average of incorrect_choice_percentage" fld="9" subtotal="average" baseField="0" baseItem="0"/>
   </dataFields>
   <conditionalFormats count="2">
+    <conditionalFormat priority="1">
+      <pivotAreas count="6">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="1"/>
+            </reference>
+            <reference field="11" count="1">
+              <x v="3"/>
+            </reference>
+          </references>
+        </pivotArea>
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="1"/>
+            </reference>
+            <reference field="11" count="1">
+              <x v="1"/>
+            </reference>
+          </references>
+        </pivotArea>
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="1"/>
+            </reference>
+            <reference field="11" count="1">
+              <x v="5"/>
+            </reference>
+          </references>
+        </pivotArea>
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="1"/>
+            </reference>
+            <reference field="11" count="1">
+              <x v="7"/>
+            </reference>
+          </references>
+        </pivotArea>
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="1"/>
+            </reference>
+            <reference field="11" count="1">
+              <x v="9"/>
+            </reference>
+          </references>
+        </pivotArea>
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="1"/>
+            </reference>
+            <reference field="11" count="1">
+              <x v="10"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
     <conditionalFormat priority="2">
       <pivotAreas count="6">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
@@ -3816,70 +4001,6 @@
           <references count="2">
             <reference field="4294967294" count="1" selected="0">
               <x v="0"/>
-            </reference>
-            <reference field="11" count="1">
-              <x v="10"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-    <conditionalFormat priority="1">
-      <pivotAreas count="6">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="2">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="1"/>
-            </reference>
-            <reference field="11" count="1">
-              <x v="3"/>
-            </reference>
-          </references>
-        </pivotArea>
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="2">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="1"/>
-            </reference>
-            <reference field="11" count="1">
-              <x v="1"/>
-            </reference>
-          </references>
-        </pivotArea>
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="2">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="1"/>
-            </reference>
-            <reference field="11" count="1">
-              <x v="5"/>
-            </reference>
-          </references>
-        </pivotArea>
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="2">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="1"/>
-            </reference>
-            <reference field="11" count="1">
-              <x v="7"/>
-            </reference>
-          </references>
-        </pivotArea>
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="2">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="1"/>
-            </reference>
-            <reference field="11" count="1">
-              <x v="9"/>
-            </reference>
-          </references>
-        </pivotArea>
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="2">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="1"/>
             </reference>
             <reference field="11" count="1">
               <x v="10"/>
@@ -4229,10 +4350,10 @@
         <v>45658</v>
       </c>
       <c r="C1" s="4"/>
-      <c r="D1" s="141" t="s">
+      <c r="D1" s="175" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="142"/>
+      <c r="E1" s="176"/>
       <c r="F1" s="6">
         <v>45717</v>
       </c>
@@ -4253,10 +4374,10 @@
         <v>45809</v>
       </c>
       <c r="O1" s="7"/>
-      <c r="P1" s="143" t="s">
+      <c r="P1" s="177" t="s">
         <v>1</v>
       </c>
-      <c r="Q1" s="144"/>
+      <c r="Q1" s="178"/>
       <c r="R1" s="3">
         <v>45839</v>
       </c>
@@ -4313,8 +4434,8 @@
       </c>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
-      <c r="D2" s="145"/>
-      <c r="E2" s="146"/>
+      <c r="D2" s="153"/>
+      <c r="E2" s="154"/>
       <c r="F2" s="18"/>
       <c r="G2" s="16"/>
       <c r="H2" s="17"/>
@@ -4327,8 +4448,8 @@
       <c r="M2" s="20"/>
       <c r="N2" s="21"/>
       <c r="O2" s="22"/>
-      <c r="P2" s="147"/>
-      <c r="Q2" s="148"/>
+      <c r="P2" s="160"/>
+      <c r="Q2" s="161"/>
       <c r="R2" s="23">
         <v>0.86</v>
       </c>
@@ -4351,8 +4472,8 @@
       <c r="AG2" s="22"/>
       <c r="AH2" s="31"/>
       <c r="AI2" s="22"/>
-      <c r="AJ2" s="149"/>
-      <c r="AK2" s="149"/>
+      <c r="AJ2" s="179"/>
+      <c r="AK2" s="179"/>
       <c r="AL2" s="32">
         <v>0.8</v>
       </c>
@@ -4369,8 +4490,8 @@
       </c>
       <c r="B3" s="36"/>
       <c r="C3" s="37"/>
-      <c r="D3" s="150"/>
-      <c r="E3" s="151"/>
+      <c r="D3" s="180"/>
+      <c r="E3" s="181"/>
       <c r="F3" s="36"/>
       <c r="G3" s="37"/>
       <c r="H3" s="38"/>
@@ -4381,8 +4502,8 @@
       <c r="M3" s="4"/>
       <c r="N3" s="36"/>
       <c r="O3" s="37"/>
-      <c r="P3" s="152"/>
-      <c r="Q3" s="153"/>
+      <c r="P3" s="182"/>
+      <c r="Q3" s="183"/>
       <c r="R3" s="40"/>
       <c r="S3" s="41"/>
       <c r="T3" s="42"/>
@@ -4401,8 +4522,8 @@
       <c r="AG3" s="37"/>
       <c r="AH3" s="38"/>
       <c r="AI3" s="37"/>
-      <c r="AJ3" s="154"/>
-      <c r="AK3" s="154"/>
+      <c r="AJ3" s="184"/>
+      <c r="AK3" s="184"/>
       <c r="AL3" s="12"/>
       <c r="AM3" s="47"/>
       <c r="AN3" s="47"/>
@@ -4413,8 +4534,8 @@
       </c>
       <c r="B4" s="36"/>
       <c r="C4" s="37"/>
-      <c r="D4" s="136"/>
-      <c r="E4" s="137"/>
+      <c r="D4" s="169"/>
+      <c r="E4" s="170"/>
       <c r="F4" s="36"/>
       <c r="G4" s="37"/>
       <c r="H4" s="38"/>
@@ -4425,8 +4546,8 @@
       <c r="M4" s="4"/>
       <c r="N4" s="36"/>
       <c r="O4" s="37"/>
-      <c r="P4" s="138"/>
-      <c r="Q4" s="139"/>
+      <c r="P4" s="172"/>
+      <c r="Q4" s="173"/>
       <c r="R4" s="40"/>
       <c r="S4" s="41"/>
       <c r="T4" s="42"/>
@@ -4445,8 +4566,8 @@
       <c r="AG4" s="37"/>
       <c r="AH4" s="38"/>
       <c r="AI4" s="37"/>
-      <c r="AJ4" s="140"/>
-      <c r="AK4" s="140"/>
+      <c r="AJ4" s="174"/>
+      <c r="AK4" s="174"/>
       <c r="AL4" s="12"/>
       <c r="AM4" s="47"/>
       <c r="AN4" s="47"/>
@@ -4457,8 +4578,8 @@
       </c>
       <c r="B5" s="36"/>
       <c r="C5" s="37"/>
-      <c r="D5" s="136"/>
-      <c r="E5" s="137"/>
+      <c r="D5" s="169"/>
+      <c r="E5" s="170"/>
       <c r="F5" s="36"/>
       <c r="G5" s="37"/>
       <c r="H5" s="38"/>
@@ -4469,8 +4590,8 @@
       <c r="M5" s="4"/>
       <c r="N5" s="36"/>
       <c r="O5" s="37"/>
-      <c r="P5" s="138"/>
-      <c r="Q5" s="139"/>
+      <c r="P5" s="172"/>
+      <c r="Q5" s="173"/>
       <c r="R5" s="40"/>
       <c r="S5" s="41">
         <v>1</v>
@@ -4493,8 +4614,8 @@
       <c r="AG5" s="37"/>
       <c r="AH5" s="38"/>
       <c r="AI5" s="37"/>
-      <c r="AJ5" s="140"/>
-      <c r="AK5" s="140"/>
+      <c r="AJ5" s="174"/>
+      <c r="AK5" s="174"/>
       <c r="AL5" s="12"/>
       <c r="AM5" s="47"/>
       <c r="AN5" s="47"/>
@@ -4505,8 +4626,8 @@
       </c>
       <c r="B6" s="36"/>
       <c r="C6" s="49"/>
-      <c r="D6" s="136"/>
-      <c r="E6" s="137"/>
+      <c r="D6" s="169"/>
+      <c r="E6" s="170"/>
       <c r="F6" s="36"/>
       <c r="G6" s="37"/>
       <c r="H6" s="38"/>
@@ -4517,8 +4638,8 @@
       <c r="M6" s="4"/>
       <c r="N6" s="36"/>
       <c r="O6" s="49"/>
-      <c r="P6" s="157"/>
-      <c r="Q6" s="158"/>
+      <c r="P6" s="140"/>
+      <c r="Q6" s="141"/>
       <c r="R6" s="40"/>
       <c r="S6" s="41"/>
       <c r="T6" s="42"/>
@@ -4539,8 +4660,8 @@
       <c r="AG6" s="49"/>
       <c r="AH6" s="56"/>
       <c r="AI6" s="49"/>
-      <c r="AJ6" s="159"/>
-      <c r="AK6" s="159"/>
+      <c r="AJ6" s="171"/>
+      <c r="AK6" s="171"/>
       <c r="AL6" s="12"/>
       <c r="AM6" s="47"/>
       <c r="AN6" s="47"/>
@@ -4551,8 +4672,8 @@
       </c>
       <c r="B7" s="55"/>
       <c r="C7" s="37"/>
-      <c r="D7" s="136"/>
-      <c r="E7" s="137"/>
+      <c r="D7" s="169"/>
+      <c r="E7" s="170"/>
       <c r="F7" s="58"/>
       <c r="G7" s="37"/>
       <c r="H7" s="38"/>
@@ -4565,8 +4686,8 @@
       <c r="M7" s="4"/>
       <c r="N7" s="55"/>
       <c r="O7" s="37"/>
-      <c r="P7" s="157"/>
-      <c r="Q7" s="158"/>
+      <c r="P7" s="140"/>
+      <c r="Q7" s="141"/>
       <c r="R7" s="40">
         <v>6</v>
       </c>
@@ -4605,8 +4726,8 @@
       </c>
       <c r="B8" s="15"/>
       <c r="C8" s="16"/>
-      <c r="D8" s="145"/>
-      <c r="E8" s="146"/>
+      <c r="D8" s="153"/>
+      <c r="E8" s="154"/>
       <c r="F8" s="15"/>
       <c r="G8" s="16"/>
       <c r="H8" s="17"/>
@@ -4617,11 +4738,11 @@
       <c r="M8" s="16"/>
       <c r="N8" s="15"/>
       <c r="O8" s="16"/>
-      <c r="P8" s="160"/>
-      <c r="Q8" s="161"/>
+      <c r="P8" s="155"/>
+      <c r="Q8" s="156"/>
       <c r="R8" s="61"/>
       <c r="S8" s="26"/>
-      <c r="T8" s="184">
+      <c r="T8" s="136">
         <v>5</v>
       </c>
       <c r="U8" s="24"/>
@@ -4641,8 +4762,8 @@
       <c r="AG8" s="16"/>
       <c r="AH8" s="17"/>
       <c r="AI8" s="16"/>
-      <c r="AJ8" s="162"/>
-      <c r="AK8" s="162"/>
+      <c r="AJ8" s="157"/>
+      <c r="AK8" s="157"/>
       <c r="AL8" s="32">
         <v>0.47</v>
       </c>
@@ -4659,8 +4780,8 @@
       </c>
       <c r="B9" s="58"/>
       <c r="C9" s="50"/>
-      <c r="D9" s="155"/>
-      <c r="E9" s="156"/>
+      <c r="D9" s="145"/>
+      <c r="E9" s="146"/>
       <c r="F9" s="58"/>
       <c r="G9" s="50"/>
       <c r="H9" s="51"/>
@@ -4671,8 +4792,8 @@
       <c r="M9" s="50"/>
       <c r="N9" s="58"/>
       <c r="O9" s="50"/>
-      <c r="P9" s="155"/>
-      <c r="Q9" s="156"/>
+      <c r="P9" s="145"/>
+      <c r="Q9" s="146"/>
       <c r="R9" s="69"/>
       <c r="S9" s="43"/>
       <c r="T9" s="70"/>
@@ -4709,8 +4830,8 @@
       </c>
       <c r="B10" s="58"/>
       <c r="C10" s="50"/>
-      <c r="D10" s="157"/>
-      <c r="E10" s="158"/>
+      <c r="D10" s="140"/>
+      <c r="E10" s="141"/>
       <c r="F10" s="58"/>
       <c r="G10" s="50"/>
       <c r="H10" s="51"/>
@@ -4721,8 +4842,8 @@
       <c r="M10" s="50"/>
       <c r="N10" s="58"/>
       <c r="O10" s="50"/>
-      <c r="P10" s="157"/>
-      <c r="Q10" s="158"/>
+      <c r="P10" s="140"/>
+      <c r="Q10" s="141"/>
       <c r="R10" s="69"/>
       <c r="S10" s="43"/>
       <c r="T10" s="70">
@@ -4761,8 +4882,8 @@
       </c>
       <c r="B11" s="58"/>
       <c r="C11" s="50"/>
-      <c r="D11" s="157"/>
-      <c r="E11" s="158"/>
+      <c r="D11" s="140"/>
+      <c r="E11" s="141"/>
       <c r="F11" s="58"/>
       <c r="G11" s="50"/>
       <c r="H11" s="51"/>
@@ -4773,8 +4894,8 @@
       <c r="M11" s="50"/>
       <c r="N11" s="58"/>
       <c r="O11" s="50"/>
-      <c r="P11" s="157"/>
-      <c r="Q11" s="158"/>
+      <c r="P11" s="140"/>
+      <c r="Q11" s="141"/>
       <c r="R11" s="69"/>
       <c r="S11" s="43"/>
       <c r="T11" s="70"/>
@@ -4811,8 +4932,8 @@
       </c>
       <c r="B12" s="58"/>
       <c r="C12" s="50"/>
-      <c r="D12" s="157"/>
-      <c r="E12" s="158"/>
+      <c r="D12" s="140"/>
+      <c r="E12" s="141"/>
       <c r="F12" s="58"/>
       <c r="G12" s="50"/>
       <c r="H12" s="51"/>
@@ -4823,8 +4944,8 @@
       <c r="M12" s="50"/>
       <c r="N12" s="58"/>
       <c r="O12" s="50"/>
-      <c r="P12" s="157"/>
-      <c r="Q12" s="158"/>
+      <c r="P12" s="140"/>
+      <c r="Q12" s="141"/>
       <c r="R12" s="69"/>
       <c r="S12" s="43"/>
       <c r="T12" s="70"/>
@@ -4861,8 +4982,8 @@
       </c>
       <c r="B13" s="58"/>
       <c r="C13" s="50"/>
-      <c r="D13" s="157"/>
-      <c r="E13" s="158"/>
+      <c r="D13" s="140"/>
+      <c r="E13" s="141"/>
       <c r="F13" s="58"/>
       <c r="G13" s="50"/>
       <c r="H13" s="51"/>
@@ -4873,8 +4994,8 @@
       <c r="M13" s="50"/>
       <c r="N13" s="58"/>
       <c r="O13" s="50"/>
-      <c r="P13" s="157"/>
-      <c r="Q13" s="158"/>
+      <c r="P13" s="140"/>
+      <c r="Q13" s="141"/>
       <c r="R13" s="69"/>
       <c r="S13" s="43"/>
       <c r="T13" s="70"/>
@@ -4913,8 +5034,8 @@
         <v>5</v>
       </c>
       <c r="C14" s="76"/>
-      <c r="D14" s="168"/>
-      <c r="E14" s="169"/>
+      <c r="D14" s="165"/>
+      <c r="E14" s="166"/>
       <c r="F14" s="78"/>
       <c r="G14" s="79"/>
       <c r="H14" s="80">
@@ -4927,8 +5048,8 @@
       <c r="M14" s="82"/>
       <c r="N14" s="15"/>
       <c r="O14" s="16"/>
-      <c r="P14" s="170"/>
-      <c r="Q14" s="171"/>
+      <c r="P14" s="167"/>
+      <c r="Q14" s="168"/>
       <c r="R14" s="18"/>
       <c r="S14" s="82"/>
       <c r="T14" s="83"/>
@@ -4947,8 +5068,8 @@
       <c r="AG14" s="82"/>
       <c r="AH14" s="83"/>
       <c r="AI14" s="82"/>
-      <c r="AJ14" s="163"/>
-      <c r="AK14" s="163"/>
+      <c r="AJ14" s="164"/>
+      <c r="AK14" s="164"/>
       <c r="AL14" s="32">
         <v>1</v>
       </c>
@@ -4967,8 +5088,8 @@
         <v>4</v>
       </c>
       <c r="C15" s="41"/>
-      <c r="D15" s="164"/>
-      <c r="E15" s="165"/>
+      <c r="D15" s="149"/>
+      <c r="E15" s="150"/>
       <c r="F15" s="69"/>
       <c r="G15" s="43"/>
       <c r="H15" s="87">
@@ -4981,8 +5102,8 @@
       <c r="M15" s="50"/>
       <c r="N15" s="58"/>
       <c r="O15" s="50"/>
-      <c r="P15" s="155"/>
-      <c r="Q15" s="156"/>
+      <c r="P15" s="145"/>
+      <c r="Q15" s="146"/>
       <c r="R15" s="58"/>
       <c r="S15" s="50"/>
       <c r="T15" s="51"/>
@@ -5019,8 +5140,8 @@
         <v>4</v>
       </c>
       <c r="C16" s="41"/>
-      <c r="D16" s="166"/>
-      <c r="E16" s="167"/>
+      <c r="D16" s="162"/>
+      <c r="E16" s="163"/>
       <c r="F16" s="69"/>
       <c r="G16" s="43"/>
       <c r="H16" s="87">
@@ -5033,8 +5154,8 @@
       <c r="M16" s="50"/>
       <c r="N16" s="58"/>
       <c r="O16" s="50"/>
-      <c r="P16" s="157"/>
-      <c r="Q16" s="158"/>
+      <c r="P16" s="140"/>
+      <c r="Q16" s="141"/>
       <c r="R16" s="58"/>
       <c r="S16" s="50"/>
       <c r="T16" s="51"/>
@@ -5071,8 +5192,8 @@
         <v>4</v>
       </c>
       <c r="C17" s="41"/>
-      <c r="D17" s="166"/>
-      <c r="E17" s="167"/>
+      <c r="D17" s="162"/>
+      <c r="E17" s="163"/>
       <c r="F17" s="69"/>
       <c r="G17" s="43"/>
       <c r="H17" s="87">
@@ -5085,8 +5206,8 @@
       <c r="M17" s="50"/>
       <c r="N17" s="58"/>
       <c r="O17" s="50"/>
-      <c r="P17" s="157"/>
-      <c r="Q17" s="158"/>
+      <c r="P17" s="140"/>
+      <c r="Q17" s="141"/>
       <c r="R17" s="58"/>
       <c r="S17" s="50"/>
       <c r="T17" s="51"/>
@@ -5123,8 +5244,8 @@
         <v>4</v>
       </c>
       <c r="C18" s="41"/>
-      <c r="D18" s="166"/>
-      <c r="E18" s="167"/>
+      <c r="D18" s="162"/>
+      <c r="E18" s="163"/>
       <c r="F18" s="69"/>
       <c r="G18" s="43"/>
       <c r="H18" s="87">
@@ -5137,8 +5258,8 @@
       <c r="M18" s="50"/>
       <c r="N18" s="58"/>
       <c r="O18" s="50"/>
-      <c r="P18" s="157"/>
-      <c r="Q18" s="158"/>
+      <c r="P18" s="140"/>
+      <c r="Q18" s="141"/>
       <c r="R18" s="58"/>
       <c r="S18" s="50"/>
       <c r="T18" s="51"/>
@@ -5175,8 +5296,8 @@
         <v>4</v>
       </c>
       <c r="C19" s="41"/>
-      <c r="D19" s="166"/>
-      <c r="E19" s="167"/>
+      <c r="D19" s="162"/>
+      <c r="E19" s="163"/>
       <c r="F19" s="69"/>
       <c r="G19" s="43"/>
       <c r="H19" s="87">
@@ -5189,8 +5310,8 @@
       <c r="M19" s="50"/>
       <c r="N19" s="58"/>
       <c r="O19" s="50"/>
-      <c r="P19" s="157"/>
-      <c r="Q19" s="158"/>
+      <c r="P19" s="140"/>
+      <c r="Q19" s="141"/>
       <c r="R19" s="58"/>
       <c r="S19" s="50"/>
       <c r="T19" s="51"/>
@@ -5225,8 +5346,8 @@
       </c>
       <c r="B20" s="15"/>
       <c r="C20" s="16"/>
-      <c r="D20" s="145"/>
-      <c r="E20" s="146"/>
+      <c r="D20" s="153"/>
+      <c r="E20" s="154"/>
       <c r="F20" s="15"/>
       <c r="G20" s="16"/>
       <c r="H20" s="17"/>
@@ -5237,8 +5358,8 @@
       <c r="M20" s="16"/>
       <c r="N20" s="15"/>
       <c r="O20" s="16"/>
-      <c r="P20" s="160"/>
-      <c r="Q20" s="161"/>
+      <c r="P20" s="155"/>
+      <c r="Q20" s="156"/>
       <c r="R20" s="15"/>
       <c r="S20" s="16"/>
       <c r="T20" s="17"/>
@@ -5259,8 +5380,8 @@
       <c r="AG20" s="63"/>
       <c r="AH20" s="89"/>
       <c r="AI20" s="90"/>
-      <c r="AJ20" s="162"/>
-      <c r="AK20" s="162"/>
+      <c r="AJ20" s="157"/>
+      <c r="AK20" s="157"/>
       <c r="AL20" s="32">
         <v>0.96</v>
       </c>
@@ -5277,8 +5398,8 @@
       </c>
       <c r="B21" s="58"/>
       <c r="C21" s="50"/>
-      <c r="D21" s="155"/>
-      <c r="E21" s="156"/>
+      <c r="D21" s="145"/>
+      <c r="E21" s="146"/>
       <c r="F21" s="58"/>
       <c r="G21" s="50"/>
       <c r="H21" s="51"/>
@@ -5289,8 +5410,8 @@
       <c r="M21" s="50"/>
       <c r="N21" s="58"/>
       <c r="O21" s="50"/>
-      <c r="P21" s="155"/>
-      <c r="Q21" s="156"/>
+      <c r="P21" s="145"/>
+      <c r="Q21" s="146"/>
       <c r="R21" s="58"/>
       <c r="S21" s="50"/>
       <c r="T21" s="51"/>
@@ -5329,8 +5450,8 @@
       </c>
       <c r="B22" s="58"/>
       <c r="C22" s="50"/>
-      <c r="D22" s="157"/>
-      <c r="E22" s="158"/>
+      <c r="D22" s="140"/>
+      <c r="E22" s="141"/>
       <c r="F22" s="58"/>
       <c r="G22" s="50"/>
       <c r="H22" s="51"/>
@@ -5341,8 +5462,8 @@
       <c r="M22" s="50"/>
       <c r="N22" s="58"/>
       <c r="O22" s="50"/>
-      <c r="P22" s="157"/>
-      <c r="Q22" s="158"/>
+      <c r="P22" s="140"/>
+      <c r="Q22" s="141"/>
       <c r="R22" s="58"/>
       <c r="S22" s="50"/>
       <c r="T22" s="51"/>
@@ -5379,8 +5500,8 @@
       </c>
       <c r="B23" s="58"/>
       <c r="C23" s="50"/>
-      <c r="D23" s="157"/>
-      <c r="E23" s="158"/>
+      <c r="D23" s="140"/>
+      <c r="E23" s="141"/>
       <c r="F23" s="58"/>
       <c r="G23" s="50"/>
       <c r="H23" s="51"/>
@@ -5391,8 +5512,8 @@
       <c r="M23" s="50"/>
       <c r="N23" s="58"/>
       <c r="O23" s="50"/>
-      <c r="P23" s="157"/>
-      <c r="Q23" s="158"/>
+      <c r="P23" s="140"/>
+      <c r="Q23" s="141"/>
       <c r="R23" s="58"/>
       <c r="S23" s="50"/>
       <c r="T23" s="51"/>
@@ -5429,8 +5550,8 @@
       </c>
       <c r="B24" s="58"/>
       <c r="C24" s="50"/>
-      <c r="D24" s="157"/>
-      <c r="E24" s="158"/>
+      <c r="D24" s="140"/>
+      <c r="E24" s="141"/>
       <c r="F24" s="58"/>
       <c r="G24" s="50"/>
       <c r="H24" s="51"/>
@@ -5441,8 +5562,8 @@
       <c r="M24" s="50"/>
       <c r="N24" s="58"/>
       <c r="O24" s="50"/>
-      <c r="P24" s="157"/>
-      <c r="Q24" s="158"/>
+      <c r="P24" s="140"/>
+      <c r="Q24" s="141"/>
       <c r="R24" s="58"/>
       <c r="S24" s="50"/>
       <c r="T24" s="51"/>
@@ -5479,8 +5600,8 @@
       </c>
       <c r="B25" s="58"/>
       <c r="C25" s="50"/>
-      <c r="D25" s="157"/>
-      <c r="E25" s="158"/>
+      <c r="D25" s="140"/>
+      <c r="E25" s="141"/>
       <c r="F25" s="58"/>
       <c r="G25" s="50"/>
       <c r="H25" s="51"/>
@@ -5491,8 +5612,8 @@
       <c r="M25" s="50"/>
       <c r="N25" s="58"/>
       <c r="O25" s="50"/>
-      <c r="P25" s="157"/>
-      <c r="Q25" s="158"/>
+      <c r="P25" s="140"/>
+      <c r="Q25" s="141"/>
       <c r="R25" s="58"/>
       <c r="S25" s="50"/>
       <c r="T25" s="51"/>
@@ -5531,8 +5652,8 @@
         <v>1</v>
       </c>
       <c r="C26" s="91"/>
-      <c r="D26" s="175"/>
-      <c r="E26" s="176"/>
+      <c r="D26" s="158"/>
+      <c r="E26" s="159"/>
       <c r="F26" s="78"/>
       <c r="G26" s="92"/>
       <c r="H26" s="80">
@@ -5547,8 +5668,8 @@
       <c r="M26" s="94"/>
       <c r="N26" s="21"/>
       <c r="O26" s="94"/>
-      <c r="P26" s="147"/>
-      <c r="Q26" s="148"/>
+      <c r="P26" s="160"/>
+      <c r="Q26" s="161"/>
       <c r="R26" s="62"/>
       <c r="S26" s="92"/>
       <c r="T26" s="95">
@@ -5573,8 +5694,8 @@
       <c r="AG26" s="94"/>
       <c r="AH26" s="97"/>
       <c r="AI26" s="94"/>
-      <c r="AJ26" s="172"/>
-      <c r="AK26" s="172"/>
+      <c r="AJ26" s="148"/>
+      <c r="AK26" s="148"/>
       <c r="AL26" s="32">
         <v>1</v>
       </c>
@@ -5593,8 +5714,8 @@
         <v>4</v>
       </c>
       <c r="C27" s="41"/>
-      <c r="D27" s="164"/>
-      <c r="E27" s="165"/>
+      <c r="D27" s="149"/>
+      <c r="E27" s="150"/>
       <c r="F27" s="69"/>
       <c r="G27" s="43"/>
       <c r="H27" s="87">
@@ -5609,8 +5730,8 @@
       <c r="M27" s="50"/>
       <c r="N27" s="58"/>
       <c r="O27" s="50"/>
-      <c r="P27" s="155"/>
-      <c r="Q27" s="156"/>
+      <c r="P27" s="145"/>
+      <c r="Q27" s="146"/>
       <c r="R27" s="69"/>
       <c r="S27" s="43"/>
       <c r="T27" s="70">
@@ -5653,8 +5774,8 @@
         <v>4</v>
       </c>
       <c r="C28" s="101"/>
-      <c r="D28" s="173"/>
-      <c r="E28" s="174"/>
+      <c r="D28" s="151"/>
+      <c r="E28" s="152"/>
       <c r="F28" s="102"/>
       <c r="G28" s="103"/>
       <c r="H28" s="104">
@@ -5669,8 +5790,8 @@
       <c r="M28" s="107"/>
       <c r="N28" s="106"/>
       <c r="O28" s="107"/>
-      <c r="P28" s="157"/>
-      <c r="Q28" s="158"/>
+      <c r="P28" s="140"/>
+      <c r="Q28" s="141"/>
       <c r="R28" s="69"/>
       <c r="S28" s="43"/>
       <c r="T28" s="70">
@@ -5711,8 +5832,8 @@
       </c>
       <c r="B29" s="15"/>
       <c r="C29" s="16"/>
-      <c r="D29" s="145"/>
-      <c r="E29" s="146"/>
+      <c r="D29" s="153"/>
+      <c r="E29" s="154"/>
       <c r="F29" s="15"/>
       <c r="G29" s="16"/>
       <c r="H29" s="17"/>
@@ -5723,8 +5844,8 @@
       <c r="M29" s="16"/>
       <c r="N29" s="15"/>
       <c r="O29" s="16"/>
-      <c r="P29" s="160"/>
-      <c r="Q29" s="161"/>
+      <c r="P29" s="155"/>
+      <c r="Q29" s="156"/>
       <c r="R29" s="15"/>
       <c r="S29" s="16"/>
       <c r="T29" s="17"/>
@@ -5745,8 +5866,8 @@
       <c r="AG29" s="16"/>
       <c r="AH29" s="17"/>
       <c r="AI29" s="16"/>
-      <c r="AJ29" s="162"/>
-      <c r="AK29" s="162"/>
+      <c r="AJ29" s="157"/>
+      <c r="AK29" s="157"/>
       <c r="AL29" s="32">
         <v>0.63</v>
       </c>
@@ -5763,8 +5884,8 @@
       </c>
       <c r="B30" s="58"/>
       <c r="C30" s="50"/>
-      <c r="D30" s="155"/>
-      <c r="E30" s="156"/>
+      <c r="D30" s="145"/>
+      <c r="E30" s="146"/>
       <c r="F30" s="58"/>
       <c r="G30" s="50"/>
       <c r="H30" s="51"/>
@@ -5775,8 +5896,8 @@
       <c r="M30" s="50"/>
       <c r="N30" s="58"/>
       <c r="O30" s="50"/>
-      <c r="P30" s="155"/>
-      <c r="Q30" s="156"/>
+      <c r="P30" s="145"/>
+      <c r="Q30" s="146"/>
       <c r="R30" s="58"/>
       <c r="S30" s="50"/>
       <c r="T30" s="51"/>
@@ -5797,8 +5918,8 @@
       <c r="AG30" s="50"/>
       <c r="AH30" s="51"/>
       <c r="AI30" s="50"/>
-      <c r="AJ30" s="178"/>
-      <c r="AK30" s="178"/>
+      <c r="AJ30" s="147"/>
+      <c r="AK30" s="147"/>
       <c r="AL30" s="12"/>
       <c r="AM30" s="72"/>
       <c r="AN30" s="72"/>
@@ -5809,8 +5930,8 @@
       </c>
       <c r="B31" s="58"/>
       <c r="C31" s="50"/>
-      <c r="D31" s="157"/>
-      <c r="E31" s="158"/>
+      <c r="D31" s="140"/>
+      <c r="E31" s="141"/>
       <c r="F31" s="58"/>
       <c r="G31" s="50"/>
       <c r="H31" s="51"/>
@@ -5821,8 +5942,8 @@
       <c r="M31" s="50"/>
       <c r="N31" s="58"/>
       <c r="O31" s="50"/>
-      <c r="P31" s="157"/>
-      <c r="Q31" s="158"/>
+      <c r="P31" s="140"/>
+      <c r="Q31" s="141"/>
       <c r="R31" s="58"/>
       <c r="S31" s="50"/>
       <c r="T31" s="51"/>
@@ -5859,8 +5980,8 @@
       </c>
       <c r="B32" s="58"/>
       <c r="C32" s="50"/>
-      <c r="D32" s="157"/>
-      <c r="E32" s="158"/>
+      <c r="D32" s="140"/>
+      <c r="E32" s="141"/>
       <c r="F32" s="58"/>
       <c r="G32" s="50"/>
       <c r="H32" s="51"/>
@@ -5871,8 +5992,8 @@
       <c r="M32" s="50"/>
       <c r="N32" s="58"/>
       <c r="O32" s="50"/>
-      <c r="P32" s="157"/>
-      <c r="Q32" s="158"/>
+      <c r="P32" s="140"/>
+      <c r="Q32" s="141"/>
       <c r="R32" s="58"/>
       <c r="S32" s="50"/>
       <c r="T32" s="51"/>
@@ -5893,8 +6014,8 @@
       <c r="AG32" s="50"/>
       <c r="AH32" s="51"/>
       <c r="AI32" s="50"/>
-      <c r="AJ32" s="177"/>
-      <c r="AK32" s="177"/>
+      <c r="AJ32" s="142"/>
+      <c r="AK32" s="142"/>
       <c r="AL32" s="111"/>
       <c r="AM32" s="72"/>
       <c r="AN32" s="72"/>
@@ -5905,8 +6026,8 @@
       </c>
       <c r="B33" s="58"/>
       <c r="C33" s="50"/>
-      <c r="D33" s="157"/>
-      <c r="E33" s="158"/>
+      <c r="D33" s="140"/>
+      <c r="E33" s="141"/>
       <c r="F33" s="58"/>
       <c r="G33" s="50"/>
       <c r="H33" s="51"/>
@@ -5917,8 +6038,8 @@
       <c r="M33" s="50"/>
       <c r="N33" s="58"/>
       <c r="O33" s="50"/>
-      <c r="P33" s="157"/>
-      <c r="Q33" s="158"/>
+      <c r="P33" s="140"/>
+      <c r="Q33" s="141"/>
       <c r="R33" s="58"/>
       <c r="S33" s="50"/>
       <c r="T33" s="51"/>
@@ -5955,8 +6076,8 @@
       </c>
       <c r="B34" s="58"/>
       <c r="C34" s="50"/>
-      <c r="D34" s="157"/>
-      <c r="E34" s="158"/>
+      <c r="D34" s="140"/>
+      <c r="E34" s="141"/>
       <c r="F34" s="58"/>
       <c r="G34" s="50"/>
       <c r="H34" s="51"/>
@@ -5967,8 +6088,8 @@
       <c r="M34" s="50"/>
       <c r="N34" s="58"/>
       <c r="O34" s="50"/>
-      <c r="P34" s="157"/>
-      <c r="Q34" s="158"/>
+      <c r="P34" s="140"/>
+      <c r="Q34" s="141"/>
       <c r="R34" s="58"/>
       <c r="S34" s="50"/>
       <c r="T34" s="51"/>
@@ -5987,8 +6108,8 @@
       <c r="AG34" s="50"/>
       <c r="AH34" s="51"/>
       <c r="AI34" s="50"/>
-      <c r="AJ34" s="177"/>
-      <c r="AK34" s="177"/>
+      <c r="AJ34" s="142"/>
+      <c r="AK34" s="142"/>
       <c r="AL34" s="111"/>
       <c r="AM34" s="72"/>
       <c r="AN34" s="72"/>
@@ -5999,8 +6120,8 @@
       </c>
       <c r="B35" s="58"/>
       <c r="C35" s="50"/>
-      <c r="D35" s="157"/>
-      <c r="E35" s="158"/>
+      <c r="D35" s="140"/>
+      <c r="E35" s="141"/>
       <c r="F35" s="58"/>
       <c r="G35" s="50"/>
       <c r="H35" s="51"/>
@@ -6011,8 +6132,8 @@
       <c r="M35" s="50"/>
       <c r="N35" s="58"/>
       <c r="O35" s="50"/>
-      <c r="P35" s="157"/>
-      <c r="Q35" s="158"/>
+      <c r="P35" s="140"/>
+      <c r="Q35" s="141"/>
       <c r="R35" s="58"/>
       <c r="S35" s="50"/>
       <c r="T35" s="51"/>
@@ -6051,8 +6172,8 @@
       </c>
       <c r="B36" s="58"/>
       <c r="C36" s="50"/>
-      <c r="D36" s="157"/>
-      <c r="E36" s="158"/>
+      <c r="D36" s="140"/>
+      <c r="E36" s="141"/>
       <c r="F36" s="58"/>
       <c r="G36" s="50"/>
       <c r="H36" s="51"/>
@@ -6063,8 +6184,8 @@
       <c r="M36" s="50"/>
       <c r="N36" s="58"/>
       <c r="O36" s="50"/>
-      <c r="P36" s="157"/>
-      <c r="Q36" s="158"/>
+      <c r="P36" s="140"/>
+      <c r="Q36" s="141"/>
       <c r="R36" s="58"/>
       <c r="S36" s="50"/>
       <c r="T36" s="51"/>
@@ -6083,8 +6204,8 @@
       <c r="AG36" s="50"/>
       <c r="AH36" s="51"/>
       <c r="AI36" s="50"/>
-      <c r="AJ36" s="177"/>
-      <c r="AK36" s="177"/>
+      <c r="AJ36" s="142"/>
+      <c r="AK36" s="142"/>
       <c r="AL36" s="111"/>
       <c r="AM36" s="72"/>
       <c r="AN36" s="72"/>
@@ -6095,8 +6216,8 @@
       </c>
       <c r="B37" s="58"/>
       <c r="C37" s="50"/>
-      <c r="D37" s="157"/>
-      <c r="E37" s="158"/>
+      <c r="D37" s="140"/>
+      <c r="E37" s="141"/>
       <c r="F37" s="58"/>
       <c r="G37" s="50"/>
       <c r="H37" s="51"/>
@@ -6107,8 +6228,8 @@
       <c r="M37" s="50"/>
       <c r="N37" s="58"/>
       <c r="O37" s="50"/>
-      <c r="P37" s="157"/>
-      <c r="Q37" s="158"/>
+      <c r="P37" s="140"/>
+      <c r="Q37" s="141"/>
       <c r="R37" s="58"/>
       <c r="S37" s="50"/>
       <c r="T37" s="51"/>
@@ -6127,8 +6248,8 @@
       <c r="AG37" s="50"/>
       <c r="AH37" s="51"/>
       <c r="AI37" s="50"/>
-      <c r="AJ37" s="177"/>
-      <c r="AK37" s="177"/>
+      <c r="AJ37" s="142"/>
+      <c r="AK37" s="142"/>
       <c r="AL37" s="111"/>
       <c r="AM37" s="72"/>
       <c r="AN37" s="72"/>
@@ -6139,8 +6260,8 @@
       </c>
       <c r="B38" s="58"/>
       <c r="C38" s="50"/>
-      <c r="D38" s="157"/>
-      <c r="E38" s="158"/>
+      <c r="D38" s="140"/>
+      <c r="E38" s="141"/>
       <c r="F38" s="58"/>
       <c r="G38" s="50"/>
       <c r="H38" s="51"/>
@@ -6151,8 +6272,8 @@
       <c r="M38" s="50"/>
       <c r="N38" s="58"/>
       <c r="O38" s="50"/>
-      <c r="P38" s="157"/>
-      <c r="Q38" s="158"/>
+      <c r="P38" s="140"/>
+      <c r="Q38" s="141"/>
       <c r="R38" s="58"/>
       <c r="S38" s="50"/>
       <c r="T38" s="51"/>
@@ -6173,8 +6294,8 @@
       <c r="AG38" s="50"/>
       <c r="AH38" s="51"/>
       <c r="AI38" s="50"/>
-      <c r="AJ38" s="177"/>
-      <c r="AK38" s="177"/>
+      <c r="AJ38" s="142"/>
+      <c r="AK38" s="142"/>
       <c r="AL38" s="111"/>
       <c r="AM38" s="72"/>
       <c r="AN38" s="72"/>
@@ -6185,8 +6306,8 @@
       </c>
       <c r="B39" s="58"/>
       <c r="C39" s="50"/>
-      <c r="D39" s="157"/>
-      <c r="E39" s="158"/>
+      <c r="D39" s="140"/>
+      <c r="E39" s="141"/>
       <c r="F39" s="58"/>
       <c r="G39" s="50"/>
       <c r="H39" s="51"/>
@@ -6197,8 +6318,8 @@
       <c r="M39" s="50"/>
       <c r="N39" s="58"/>
       <c r="O39" s="50"/>
-      <c r="P39" s="157"/>
-      <c r="Q39" s="158"/>
+      <c r="P39" s="140"/>
+      <c r="Q39" s="141"/>
       <c r="R39" s="58"/>
       <c r="S39" s="50"/>
       <c r="T39" s="51"/>
@@ -6235,8 +6356,8 @@
       </c>
       <c r="B40" s="58"/>
       <c r="C40" s="50"/>
-      <c r="D40" s="157"/>
-      <c r="E40" s="158"/>
+      <c r="D40" s="140"/>
+      <c r="E40" s="141"/>
       <c r="F40" s="58"/>
       <c r="G40" s="50"/>
       <c r="H40" s="51"/>
@@ -6247,8 +6368,8 @@
       <c r="M40" s="50"/>
       <c r="N40" s="58"/>
       <c r="O40" s="50"/>
-      <c r="P40" s="157"/>
-      <c r="Q40" s="158"/>
+      <c r="P40" s="140"/>
+      <c r="Q40" s="141"/>
       <c r="R40" s="58"/>
       <c r="S40" s="50"/>
       <c r="T40" s="51"/>
@@ -6269,8 +6390,8 @@
       <c r="AG40" s="50"/>
       <c r="AH40" s="51"/>
       <c r="AI40" s="50"/>
-      <c r="AJ40" s="177"/>
-      <c r="AK40" s="177"/>
+      <c r="AJ40" s="142"/>
+      <c r="AK40" s="142"/>
       <c r="AL40" s="111"/>
       <c r="AM40" s="72"/>
       <c r="AN40" s="72"/>
@@ -6281,8 +6402,8 @@
       </c>
       <c r="B41" s="58"/>
       <c r="C41" s="50"/>
-      <c r="D41" s="157"/>
-      <c r="E41" s="158"/>
+      <c r="D41" s="140"/>
+      <c r="E41" s="141"/>
       <c r="F41" s="58"/>
       <c r="G41" s="50"/>
       <c r="H41" s="51"/>
@@ -6293,8 +6414,8 @@
       <c r="M41" s="50"/>
       <c r="N41" s="58"/>
       <c r="O41" s="50"/>
-      <c r="P41" s="157"/>
-      <c r="Q41" s="158"/>
+      <c r="P41" s="140"/>
+      <c r="Q41" s="141"/>
       <c r="R41" s="58"/>
       <c r="S41" s="50"/>
       <c r="T41" s="51"/>
@@ -6315,8 +6436,8 @@
       <c r="AG41" s="50"/>
       <c r="AH41" s="51"/>
       <c r="AI41" s="50"/>
-      <c r="AJ41" s="177"/>
-      <c r="AK41" s="177"/>
+      <c r="AJ41" s="142"/>
+      <c r="AK41" s="142"/>
       <c r="AL41" s="111"/>
       <c r="AM41" s="72"/>
       <c r="AN41" s="72"/>
@@ -6327,8 +6448,8 @@
       </c>
       <c r="B42" s="58"/>
       <c r="C42" s="50"/>
-      <c r="D42" s="157"/>
-      <c r="E42" s="158"/>
+      <c r="D42" s="140"/>
+      <c r="E42" s="141"/>
       <c r="F42" s="58"/>
       <c r="G42" s="50"/>
       <c r="H42" s="51"/>
@@ -6339,8 +6460,8 @@
       <c r="M42" s="50"/>
       <c r="N42" s="58"/>
       <c r="O42" s="50"/>
-      <c r="P42" s="157"/>
-      <c r="Q42" s="158"/>
+      <c r="P42" s="140"/>
+      <c r="Q42" s="141"/>
       <c r="R42" s="58"/>
       <c r="S42" s="50"/>
       <c r="T42" s="51"/>
@@ -6377,8 +6498,8 @@
       </c>
       <c r="B43" s="106"/>
       <c r="C43" s="107"/>
-      <c r="D43" s="182"/>
-      <c r="E43" s="183"/>
+      <c r="D43" s="143"/>
+      <c r="E43" s="144"/>
       <c r="F43" s="106"/>
       <c r="G43" s="107"/>
       <c r="H43" s="113"/>
@@ -6389,8 +6510,8 @@
       <c r="M43" s="107"/>
       <c r="N43" s="106"/>
       <c r="O43" s="107"/>
-      <c r="P43" s="182"/>
-      <c r="Q43" s="183"/>
+      <c r="P43" s="143"/>
+      <c r="Q43" s="144"/>
       <c r="R43" s="106"/>
       <c r="S43" s="107"/>
       <c r="T43" s="51"/>
@@ -6409,8 +6530,8 @@
       <c r="AG43" s="50"/>
       <c r="AH43" s="51"/>
       <c r="AI43" s="50"/>
-      <c r="AJ43" s="177"/>
-      <c r="AK43" s="177"/>
+      <c r="AJ43" s="142"/>
+      <c r="AK43" s="142"/>
       <c r="AL43" s="111"/>
       <c r="AM43" s="114"/>
       <c r="AN43" s="114"/>
@@ -6447,10 +6568,10 @@
       <c r="O44" s="126">
         <v>4</v>
       </c>
-      <c r="P44" s="179">
+      <c r="P44" s="137">
         <v>1</v>
       </c>
-      <c r="Q44" s="180"/>
+      <c r="Q44" s="138"/>
       <c r="R44" s="125">
         <v>7</v>
       </c>
@@ -6483,38 +6604,82 @@
       <c r="AG44" s="126"/>
       <c r="AH44" s="127"/>
       <c r="AI44" s="126"/>
-      <c r="AJ44" s="181"/>
-      <c r="AK44" s="181"/>
+      <c r="AJ44" s="139"/>
+      <c r="AK44" s="139"/>
       <c r="AL44" s="128"/>
       <c r="AM44" s="129"/>
       <c r="AN44" s="129"/>
     </row>
   </sheetData>
   <mergeCells count="107">
-    <mergeCell ref="P44:Q44"/>
-    <mergeCell ref="AJ44:AK44"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="P41:Q41"/>
-    <mergeCell ref="AJ41:AK41"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="P42:Q42"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="P43:Q43"/>
-    <mergeCell ref="AJ43:AK43"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="P38:Q38"/>
-    <mergeCell ref="AJ38:AK38"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="P39:Q39"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="P40:Q40"/>
-    <mergeCell ref="AJ40:AK40"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="P36:Q36"/>
-    <mergeCell ref="AJ36:AK36"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="P37:Q37"/>
-    <mergeCell ref="AJ37:AK37"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="AJ4:AK4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="AJ5:AK5"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="AJ2:AK2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="AJ3:AK3"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="P11:Q11"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="AJ6:AK6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="AJ8:AK8"/>
+    <mergeCell ref="AJ14:AK14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="P15:Q15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="P17:Q17"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="AJ20:AK20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="P21:Q21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="P22:Q22"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="P23:Q23"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="P18:Q18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="P19:Q19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="P20:Q20"/>
+    <mergeCell ref="AJ26:AK26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="P27:Q27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="P28:Q28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="P29:Q29"/>
+    <mergeCell ref="AJ29:AK29"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="P24:Q24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="P25:Q25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="P26:Q26"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="P33:Q33"/>
     <mergeCell ref="D34:E34"/>
@@ -6530,74 +6695,30 @@
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="P32:Q32"/>
     <mergeCell ref="AJ32:AK32"/>
-    <mergeCell ref="AJ26:AK26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="P27:Q27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="P28:Q28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="P29:Q29"/>
-    <mergeCell ref="AJ29:AK29"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="P24:Q24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="P25:Q25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="P26:Q26"/>
-    <mergeCell ref="AJ20:AK20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="P21:Q21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="P22:Q22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="P23:Q23"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="P18:Q18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="P19:Q19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="P20:Q20"/>
-    <mergeCell ref="AJ14:AK14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="P15:Q15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="P17:Q17"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="P11:Q11"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="AJ6:AK6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="AJ8:AK8"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="AJ4:AK4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="AJ5:AK5"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="AJ2:AK2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="AJ3:AK3"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="P38:Q38"/>
+    <mergeCell ref="AJ38:AK38"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="P39:Q39"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="P40:Q40"/>
+    <mergeCell ref="AJ40:AK40"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="P36:Q36"/>
+    <mergeCell ref="AJ36:AK36"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="P37:Q37"/>
+    <mergeCell ref="AJ37:AK37"/>
+    <mergeCell ref="P44:Q44"/>
+    <mergeCell ref="AJ44:AK44"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="P41:Q41"/>
+    <mergeCell ref="AJ41:AK41"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="P42:Q42"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="P43:Q43"/>
+    <mergeCell ref="AJ43:AK43"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9081,7 +9202,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting pivot="1" sqref="B6 B5 B7 B8 B9 B10">
+  <conditionalFormatting pivot="1" sqref="B5 B6 B7 B8 B9 B10">
     <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="min"/>
@@ -9095,7 +9216,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting pivot="1" sqref="C5 C6 C7 C8 C9 C10">
+  <conditionalFormatting pivot="1" sqref="C6 C5 C7 C8 C9 C10">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
@@ -9124,7 +9245,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>B6 B5 B7 B8 B9 B10</xm:sqref>
+          <xm:sqref>B5 B6 B7 B8 B9 B10</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" pivot="1">
           <x14:cfRule type="dataBar" id="{2BAAA5BF-4CE1-4F93-8D6D-87F551054ABB}">
@@ -9139,10 +9260,228 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>C5 C6 C7 C8 C9 C10</xm:sqref>
+          <xm:sqref>C6 C5 C7 C8 C9 C10</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A673585F-C3C3-46A1-8C29-9D0047C3F585}">
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultRowHeight="30" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="91.42578125" style="185" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" s="185" customFormat="1" ht="30" customHeight="1" thickBot="1">
+      <c r="A1" s="115" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="186" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="187" t="s">
+        <v>94</v>
+      </c>
+      <c r="D1" s="185" t="s">
+        <v>93</v>
+      </c>
+      <c r="E1" s="188" t="s">
+        <v>95</v>
+      </c>
+      <c r="F1" s="185" t="s">
+        <v>96</v>
+      </c>
+      <c r="G1" s="188" t="s">
+        <v>97</v>
+      </c>
+      <c r="H1" s="185" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="30" customHeight="1" thickTop="1">
+      <c r="A2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" s="185" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="30" customHeight="1">
+      <c r="A3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" s="185" t="s">
+        <v>63</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="30" customHeight="1">
+      <c r="A4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="185" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="30" customHeight="1">
+      <c r="A5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" s="185" t="s">
+        <v>65</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="30" customHeight="1">
+      <c r="A6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" s="185" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="30" customHeight="1">
+      <c r="A7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7" s="185" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="30" customHeight="1">
+      <c r="A8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" s="185" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="30" customHeight="1">
+      <c r="A9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" s="185" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="30" customHeight="1">
+      <c r="A10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" s="185" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="30" customHeight="1">
+      <c r="A11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B11" s="185" t="s">
+        <v>72</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="30" customHeight="1">
+      <c r="A12" t="s">
+        <v>88</v>
+      </c>
+      <c r="B12" s="185" t="s">
+        <v>68</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="30" customHeight="1">
+      <c r="A13" t="s">
+        <v>89</v>
+      </c>
+      <c r="B13" s="185" t="s">
+        <v>73</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="30" customHeight="1">
+      <c r="A14" t="s">
+        <v>90</v>
+      </c>
+      <c r="B14" s="185" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="30" customHeight="1">
+      <c r="A15" t="s">
+        <v>91</v>
+      </c>
+      <c r="B15" s="185" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="30" customHeight="1">
+      <c r="A16" t="s">
+        <v>92</v>
+      </c>
+      <c r="B16" s="185" t="s">
+        <v>76</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="C2:CC16">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>